--- a/신고신저가_20260818.xlsx
+++ b/신고신저가_20260818.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="164" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <color rgb="000000C0"/>
     </font>
@@ -76,15 +77,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -453,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -611,7 +616,74 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>💬 ■ 결론: 미국은 지수(-0.5%)보다 내부가 갈렸다 — 신고가 60에 신저가 16(신규 14)인데 신규 신저가 14종 중 7종이 소비재·유통이고 신규 신고가는 에너지·금·은행에 몰림. 반대로 아시아는 D램(창신메모리 +12%)과 해운(호르무즈 운임)이 끌어올린 하루. 네 시장 공통 축은 실물자산·리플레이션이고 공통 반대편은 소비와 금리민감 자산인 국면(추정), 판정은 오늘밤 홈디포부터 열리는 유통 실적 주간이 낸다</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>■ 美(8/17): S&amp;P500 7,745.06 -0.52%·나스닥 26,644.91 -0.32%·다우 53,459.78 -0.51%, 52주 위치 96%. 신고가 60(신규 28)·신저가 16(신규 14)로 전 거래일 81/8 대비 폭이 눈에 띄게 좁아짐. 신규 신저가 명단이 이번 스캔의 본론 — 나이키 -4.0%·데커스 -3.2%·아머스포츠 -0.9%·딕스스포팅 -2.8%·이베이 -2.1%·알트리아 -2.7%에 스텔란티스 -4.5%(카메라 결함 848만대 리콜)까지 소비·유통이 무더기. 여기에 아파트·게이밍 리츠(에쿼티레지덴셜 -3.5%, VICI -1.5%, GLPI -3.0%)가 붙어 소비＋금리민감의 이중 이탈. 반대편 신규 신고가는 에너지(세노버스 +3.6·퍼미안 +3.2·APA +2.7·HF싱클레어 +1.4)와 금광(아이엠골드 +4.1·뉴몬트 +2.2·엘도라도 +1.5·애그니코이글 +1.2), 대형은행(BAC·USB·PNC·M&amp;T·스테이트스트리트·BNY멜론)에 집중. 순강도는 금융 +16(12MF PER 중앙값 15.0, 표본 160/164), 에너지광물 +9(10.9, 22/22), 헬스테크 +4(19.0), 비에너지광물 +4(16.2) / 약세는 소매유통 -2(19.8), 소비내구재 -1(15.9). 다만 ETF는 당일 XLE +1.1%만 뚜렷하고 XLF -1.0%로 순강도와 방향이 엇갈림 — 금융 신고가는 오늘 상승이 아니라 누적 레벨의 잔상. XLK +0.2 / XLC -1.9·XLP -1.6·XLY -1.2·XLRE -1.0. XLE는 주간 +4.0%·YTD 41.9%로 1위 고수</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ 日(8/17): 닛케이225 69,220.25 +0.74%로 사상 최고치 경신, 5거래일 연속 상승. 신고가 13(신규 3)·신저가 1(신규 1). 신규 신고가는 혼다 +1.8%(8/5 1분기 영업익 +117%·가이던스 상향 이후 목표주가 상향 랠리), MS&amp;AD +1.8%(1분기 호실적 여진), 야마하모터. 업종 ETF는 철강·비철 +4.0% 독주(주간 +8.6%·YTD 59.2% 1위) / 상사·도매 -1.7%·의약 -1.6%·소매 -1.3%. 순강도 소비내구재 +3·운수 +3(상선미쓰이 +2.4·닛폰유센 +1.4·가와사키기선 +1.4로 해운 3사 승계 신고가)·금융 +1. 유일한 신규 신저가가 스미토모부동산 -0.7% — 30년물 국채금리 최고치와 일본은행 추가 인상 경계가 부동산으로 먼저 나옴(부동산 ETF 1개월 -9.0%). 금리 상승이 은행(YTD 49.5%)엔 연료, 부동산엔 독인 구도가 선명</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>■ 홍콩(8/17): 항셍 25,453.23 +1.34%·항셍테크 4,782.03 +1.58%로 반등. 다만 주간은 항셍 -1.9%·항셍테크 -2.8%이고 항셍테크 YTD -12.8%·52주 위치 22%라 중화권 최약 지위는 그대로. 신고가 10(신규 8)·신저가 1. 신규 신고가가 두 갈래 — AI 하드웨어(중지쉬촹 +8.2%, 800G→1.6T 전환 기대와 열관리업체 지분인수 공시 / 넥스칩 +6.0%, 국산화 기대)와 해운(OOIL +7.3%·코스코 H +6.1%·SITC +4.0%), 여기에 위탁연구개발(우시앱텍 H +3.0%·팜아론 +2.6%)이 붙음. 순강도 운수 +3(12MF 10.5, 표본 5/13)·전자기술 +2(21.0, 13/17)·헬스테크 +2(29.6). 유일한 신저가는 콰이쇼우 — 전자상거래 거래액 성장 둔화 우려로 8/20 실적발표 전 신저가</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>■ 中(8/17): 상해종합 3,982.65 +1.41%·CSI300 4,741.10 +1.61%로 사흘 보합을 깨고 급등, 상해종합은 4,000선 목전. 신고가 3(전부 신규)·신저가 1. 창신메모리 +12.0%가 이날의 중심 — AI발 메모리 슈퍼사이클과 D램 가격 급등이 중국 유일 D램 양산업체로 직결. 우시앱텍 A +4.8%(상반기 매출 +39%·순이익 +29%), 코스코 A +3.8%로 A주·H주가 같은 종목에서 동시에 신고가를 낸 것이 특징. 업종 ETF는 반도체 +5.1%(YTD 54.6% 1위)·5G통신 +4.0%(47.2%)·테크 +3.5%(38.2%)·유색금속 +3.1%(1개월 +19.1%) / 백주 -2.5%(YTD -19.8% 꼴찌)·소비 -0.9%로 성장 대 소비의 갈림이 전 거래일보다 더 벌어짐. 순강도는 표본이 얇아(전자기술 12MF 38/72) 밸류 절대수준 인용은 보류</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>■ 체크: ①8/18(화) 홈디포 컨센 EPS 4.73달러 — 신규 신저가 14종 중 7종이 소비·유통에 몰린 상태에서 나오는 첫 실물 확인, 8/19 타깃·8/20 월마트로 이어지는 주간의 방향타 ②메모리·광모듈 축의 지속성 — 창신메모리 +12%·중지쉬촹 +8.2%·A주 반도체 ETF +5.1%가 하루짜리 가격 뉴스인지 8/26 엔비디아까지 이어지는 사이클 확인인지, A주 반도체 ETF의 1개월 조정 여부가 1차 단서 ③호르무즈 운임 — 해운주가 미·일·중·홍콩 4개 시장에서 동시 신고가를 낸 만큼 이미 컨센이나, 운임 상승이 인플레로 되돌아오면 8/19 FOMC 회의록·금리 경로에 역풍이라 양방향</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>■ 참고: 08:07 KST 실행 — 미국은 8/17(월) ET 16:00 마감분으로 약 3시간 전 확정, 일본·홍콩·중국A는 8/17 마감분(오늘 개장 전)이라 전 시장 정상 갱신. 스크립트가 만든 index CSV의 닛케이225·KOSPI는 8/14로 갱신이 밀려 있어 닛케이 8/17 종가는 별도 확인값(69,220.25 +0.74%)을 사용. ETF 44/44·지수 8/8 수집 정상, 12MF PER은 TradingView 선행 배수. 에쿼티레지덴셜 신저가는 아발론베이와의 대등합병이 8/17 완료돼 8/18부터 Vivmark(VMRK)로 전환되는 데 따른 처리 신호로 판단, 펀더멘털 악화 신호로 읽지 말 것. 회사PC 자격증명 부재로 vault pull 실패해 텔레그램 적재분 미사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>
@@ -709,19 +781,19 @@
       <c r="C2" t="n">
         <v>7745.06</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="4" t="n">
         <v>-0.52</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="4" t="n">
         <v>-0.1</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="5" t="n">
         <v>3.85</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="5" t="n">
         <v>4.54</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="5" t="n">
         <v>13.14</v>
       </c>
       <c r="I2" t="n">
@@ -747,19 +819,19 @@
       <c r="C3" t="n">
         <v>26644.91</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="4" t="n">
         <v>-0.32</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="5" t="n">
         <v>4.41</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="5" t="n">
         <v>1.6</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="5" t="n">
         <v>14.64</v>
       </c>
       <c r="I3" t="n">
@@ -785,19 +857,19 @@
       <c r="C4" t="n">
         <v>6977.94</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="5" t="n">
         <v>2.42</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="5" t="n">
         <v>11.49</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="4" t="n">
         <v>-4.21</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="4" t="n">
         <v>-12.57</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" s="5" t="n">
         <v>65.58</v>
       </c>
       <c r="I4" t="n">
@@ -823,19 +895,19 @@
       <c r="C5" t="n">
         <v>68713.8</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="5" t="n">
         <v>0.59</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="5" t="n">
         <v>4.61</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="5" t="n">
         <v>1.43</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="5" t="n">
         <v>11.89</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="5" t="n">
         <v>36.5</v>
       </c>
       <c r="I5" t="n">
@@ -861,19 +933,19 @@
       <c r="C6" t="n">
         <v>3982.65</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="5" t="n">
         <v>1.41</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="5" t="n">
         <v>0.4</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="5" t="n">
         <v>5.8</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="4" t="n">
         <v>-4.48</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="5" t="n">
         <v>0.35</v>
       </c>
       <c r="I6" t="n">
@@ -899,19 +971,19 @@
       <c r="C7" t="n">
         <v>4741.1</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="5" t="n">
         <v>1.61</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="5" t="n">
         <v>0.83</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="5" t="n">
         <v>4.68</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="4" t="n">
         <v>-2.3</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="5" t="n">
         <v>2.4</v>
       </c>
       <c r="I7" t="n">
@@ -937,19 +1009,19 @@
       <c r="C8" t="n">
         <v>25453.23</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="5" t="n">
         <v>1.34</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="4" t="n">
         <v>-1.87</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="5" t="n">
         <v>3.63</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="4" t="n">
         <v>-1.96</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="4" t="n">
         <v>-0.6899999999999999</v>
       </c>
       <c r="I8" t="n">
@@ -975,19 +1047,19 @@
       <c r="C9" t="n">
         <v>4782.03</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="5" t="n">
         <v>1.58</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="4" t="n">
         <v>-2.79</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="5" t="n">
         <v>3.44</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="4" t="n">
         <v>-3.22</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="4" t="n">
         <v>-13.31</v>
       </c>
       <c r="I9" t="n">
@@ -1106,7 +1178,7 @@
       <c r="F2" t="n">
         <v>16</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1147,7 +1219,7 @@
       <c r="F3" t="n">
         <v>9</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1188,7 +1260,7 @@
       <c r="F4" t="n">
         <v>4</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1229,7 +1301,7 @@
       <c r="F5" t="n">
         <v>4</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1270,7 +1342,7 @@
       <c r="F6" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1311,7 +1383,7 @@
       <c r="F7" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1352,7 +1424,7 @@
       <c r="F8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1393,7 +1465,7 @@
       <c r="F9" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1434,7 +1506,7 @@
       <c r="F10" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1475,7 +1547,7 @@
       <c r="F11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1516,7 +1588,7 @@
       <c r="F12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1557,7 +1629,7 @@
       <c r="F13" t="n">
         <v>-1</v>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1598,7 +1670,7 @@
       <c r="F14" t="n">
         <v>-2</v>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1924,7 +1996,7 @@
       <c r="F22" t="n">
         <v>3</v>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1965,7 +2037,7 @@
       <c r="F23" t="n">
         <v>3</v>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2004,7 +2076,7 @@
       <c r="F24" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2043,7 +2115,7 @@
       <c r="F25" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2082,7 +2154,7 @@
       <c r="F26" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2123,7 +2195,7 @@
       <c r="F27" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2162,7 +2234,7 @@
       <c r="F28" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2203,7 +2275,7 @@
       <c r="F29" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2677,7 +2749,7 @@
       <c r="F41" t="n">
         <v>3</v>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2718,7 +2790,7 @@
       <c r="F42" t="n">
         <v>2</v>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2759,7 +2831,7 @@
       <c r="F43" t="n">
         <v>2</v>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2800,7 +2872,7 @@
       <c r="F44" t="n">
         <v>1</v>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="G44" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2839,7 +2911,7 @@
       <c r="F45" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="G45" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2880,7 +2952,7 @@
       <c r="F46" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="G46" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2919,7 +2991,7 @@
       <c r="F47" t="n">
         <v>-1</v>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3395,7 +3467,7 @@
       <c r="F59" t="n">
         <v>1</v>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3436,7 +3508,7 @@
       <c r="F60" t="n">
         <v>1</v>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3477,7 +3549,7 @@
       <c r="F61" t="n">
         <v>1</v>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="G61" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3516,7 +3588,7 @@
       <c r="F62" t="n">
         <v>-1</v>
       </c>
-      <c r="G62" s="5" t="inlineStr">
+      <c r="G62" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -4099,30 +4171,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="95" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4143,90 +4216,95 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>1D</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>1주</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>YTD26</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>순위26</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>YTD25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>순위25</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>YTD24</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>순위24</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>YTD23</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>순위23</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>YTD22</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>순위22</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>YTD21</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>순위21</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YTD20</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>순위20</t>
         </is>
@@ -4248,58 +4326,63 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>+0.2%로 대형 지수 하락장에서 유일하게 버팀. 전자기술 순강도 +2에 그쳐 폭은 좁고 YTD 32.5% 2위는 유지</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="F2" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="G2" s="9" t="n">
         <v>8.4</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="H2" s="9" t="n">
         <v>8.1</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="I2" s="9" t="n">
         <v>32.5</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="K2" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="M2" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="6" t="n">
+      <c r="O2" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="Q2" s="9" t="n">
         <v>-27.7</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>9</v>
       </c>
-      <c r="R2" s="6" t="n">
+      <c r="S2" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>4</v>
       </c>
-      <c r="T2" s="6" t="n">
+      <c r="U2" s="9" t="n">
         <v>43.6</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4319,58 +4402,63 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>-0.2%지만 헬스테크 순강도 +4로 신고가는 계속 나옴(레볼루션메디슨스 +4.1%). 3개월 +15.6%로 중기 모멘텀 최상위</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="9" t="n">
         <v>3.7</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="H3" s="9" t="n">
         <v>15.6</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="I3" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>7</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="K3" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="n">
+      <c r="O3" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="Q3" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>4</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="S3" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="T3" s="6" t="n">
+      <c r="U3" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4390,58 +4478,63 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>-1.0%인데 금융 순강도 +16으로 압도적 1위 — 오늘 상승이 아니라 누적 레벨의 잔상. 대형은행 6종 신규 신고가, 12MF PER 15.0</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="O4" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>7</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" s="9" t="n">
         <v>-10.6</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" s="9" t="n">
         <v>34.8</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="U4" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4461,58 +4554,63 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>-1.2%·YTD -1.8% 11개 중 10위. 나이키·데커스·딕스 등 소비 신저가 무더기의 진원, 8/18 홈디포가 1차 판정</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="9" t="n">
         <v>-1.8</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" s="9" t="n">
         <v>26.5</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="O5" s="9" t="n">
         <v>39.6</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="Q5" s="9" t="n">
         <v>-36.3</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>10</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="S5" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="U5" s="9" t="n">
         <v>29.6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4532,58 +4630,63 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>-1.9%로 당일 최약·YTD -5.3% 꼴찌. 3개월 -4.3%로 유일한 마이너스, 소외 지속</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
         <v>-1.9</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H6" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="I6" s="9" t="n">
         <v>-5.3</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="M6" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="O6" s="9" t="n">
         <v>52.8</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="Q6" s="9" t="n">
         <v>-37.6</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="S6" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" s="6" t="n">
+      <c r="U6" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4603,58 +4706,63 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>-0.1%로 방어. 산업서비스 순강도 +3·생산제조 +2로 내부는 양호, 3개월 +9.0%</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F7" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="G7" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="H7" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="I7" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="O7" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="Q7" s="9" t="n">
         <v>-5.6</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>5</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="S7" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="T7" s="6" t="n">
+      <c r="U7" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4674,58 +4782,63 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>-1.6%로 하위권. 알트리아 -2.7% 신저가 등 필수소비재 순강도 0의 혼조가 가격으로 나옴</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="F8" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="H8" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I8" s="9" t="n">
         <v>10.4</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>6</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K8" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="M8" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="O8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="Q8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="S8" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>10</v>
       </c>
-      <c r="T8" s="6" t="n">
+      <c r="U8" s="9" t="n">
         <v>10.1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4745,58 +4858,63 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>+1.1% 당일 1위·주간 +4.0%·YTD 41.9% 압도적 1위. 호르무즈 리스크로 에너지광물 순강도 +9, 12MF PER 10.9로 여전히 최저 배수</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="F9" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="G9" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="H9" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="I9" s="9" t="n">
         <v>41.9</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="M9" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="O9" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>9</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="Q9" s="9" t="n">
         <v>64.3</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="S9" s="9" t="n">
         <v>53.3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="6" t="n">
+      <c r="U9" s="9" t="n">
         <v>-32.7</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4816,58 +4934,63 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>-0.3%·1개월 -2.2%로 정체. 금리 상승 국면에서 방어 프리미엄이 약해진 구간(추정)</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="F10" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="G10" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="H10" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="I10" s="9" t="n">
         <v>4.9</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>9</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="K10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="M10" s="9" t="n">
         <v>23.3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="O10" s="9" t="n">
         <v>-7.2</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>11</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="Q10" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="S10" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="T10" s="6" t="n">
+      <c r="U10" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4887,58 +5010,63 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>-0.6%지만 비에너지광물 순강도 +4 — 뉴몬트·애그니코이글 등 금광이 소재 신고가를 혼자 만들고 있음</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="F11" s="9" t="n">
         <v>-1.8</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="G11" s="9" t="n">
         <v>3.4</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="H11" s="9" t="n">
         <v>4.2</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="I11" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>4</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="9" t="n">
         <v>9.9</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="O11" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="Q11" s="9" t="n">
         <v>-12.3</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="S11" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="U11" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4958,58 +5086,63 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>-1.0%·1개월 -1.3%. 아파트·게이밍 리츠 3종(에쿼티레지덴셜·VICI·GLPI) 신저가로 금리민감 이탈 확인</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="F12" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="G12" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="H12" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="I12" s="9" t="n">
         <v>12.8</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>5</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="K12" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="M12" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="O12" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="Q12" s="9" t="n">
         <v>-26.2</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>8</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="S12" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="U12" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5029,58 +5162,59 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="F13" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="G13" s="9" t="n">
         <v>5.4</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="H13" s="9" t="n">
         <v>10.3</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="I13" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>7</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="K13" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>15</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="M13" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="O13" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>13</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="Q13" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>10</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="S13" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>11</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="U13" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5100,58 +5234,59 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="8" t="inlineStr"/>
+      <c r="E14" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="F14" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="9" t="n">
         <v>5.4</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="H14" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="I14" s="9" t="n">
         <v>18.2</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>8</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="K14" s="9" t="n">
         <v>41.4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="9" t="n">
         <v>29.9</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="O14" s="9" t="n">
         <v>37.2</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="Q14" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="S14" s="9" t="n">
         <v>39.3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="U14" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>17</v>
       </c>
     </row>
@@ -5171,58 +5306,59 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="8" t="inlineStr"/>
+      <c r="E15" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="F15" s="9" t="n">
         <v>2.7</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="G15" s="9" t="n">
         <v>-5</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="H15" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="I15" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>11</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="K15" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="M15" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="O15" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>9</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="Q15" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>12</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="S15" s="9" t="n">
         <v>12.6</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>8</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="U15" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5242,58 +5378,59 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="F16" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="G16" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="H16" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="I16" s="9" t="n">
         <v>24.1</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>6</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="K16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>17</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="M16" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>16</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="O16" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>12</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="Q16" s="9" t="n">
         <v>-9.4</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>14</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="S16" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>14</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="U16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5313,58 +5450,59 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="F17" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="9" t="n">
         <v>2.7</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="H17" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="I17" s="9" t="n">
         <v>2.9</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>14</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="K17" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>16</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="M17" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>13</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="O17" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>17</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="Q17" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="S17" s="9" t="n">
         <v>-8.4</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>17</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="U17" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5384,58 +5522,59 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="F18" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="G18" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="H18" s="9" t="n">
         <v>7.6</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="I18" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>16</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="K18" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>14</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="M18" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>11</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="O18" s="9" t="n">
         <v>40.5</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="Q18" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>16</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="S18" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="T18" s="6" t="n">
+      <c r="U18" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5455,58 +5594,59 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="F19" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="G19" s="9" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="H19" s="9" t="n">
         <v>-2.5</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="I19" s="9" t="n">
         <v>59.2</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="K19" s="9" t="n">
         <v>68.8</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="M19" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="O19" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>4</v>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="Q19" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="S19" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="U19" s="9" t="n">
         <v>-8.6</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5526,58 +5666,59 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="8" t="inlineStr"/>
+      <c r="E20" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="F20" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="G20" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="H20" s="9" t="n">
         <v>4.2</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="I20" s="9" t="n">
         <v>24.4</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>5</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="K20" s="9" t="n">
         <v>31.1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="M20" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="O20" s="9" t="n">
         <v>33.9</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="Q20" s="9" t="n">
         <v>-9.9</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>15</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="S20" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>9</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="U20" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5597,58 +5738,59 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="F21" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="G21" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="H21" s="9" t="n">
         <v>14.7</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="I21" s="9" t="n">
         <v>41.3</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>3</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="K21" s="9" t="n">
         <v>27.5</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="M21" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>10</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="O21" s="9" t="n">
         <v>33.7</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>7</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="Q21" s="9" t="n">
         <v>-23</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>17</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="S21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>5</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="U21" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5668,58 +5810,59 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="8" t="inlineStr"/>
+      <c r="E22" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="F22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="G22" s="9" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="H22" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="I22" s="9" t="n">
         <v>15.2</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>10</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="K22" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>13</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="M22" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="O22" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>15</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="Q22" s="9" t="n">
         <v>-5.9</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>13</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="S22" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>13</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="U22" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5739,58 +5882,59 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="8" t="inlineStr"/>
+      <c r="E23" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="F23" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="G23" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="H23" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="I23" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>15</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="K23" s="9" t="n">
         <v>37.4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>7</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="M23" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>15</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="O23" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="Q23" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>7</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="S23" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>16</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="U23" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5810,58 +5954,59 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="8" t="inlineStr"/>
+      <c r="E24" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="F24" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="G24" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="H24" s="9" t="n">
         <v>5.7</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="I24" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>12</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="K24" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>11</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="M24" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>17</v>
       </c>
-      <c r="N24" s="6" t="n">
+      <c r="O24" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>14</v>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="Q24" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>8</v>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="S24" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>12</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="U24" s="9" t="n">
         <v>-17.1</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5881,58 +6026,59 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="F25" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="G25" s="9" t="n">
         <v>3.7</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="H25" s="9" t="n">
         <v>-6.8</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="I25" s="9" t="n">
         <v>16.7</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>9</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="K25" s="9" t="n">
         <v>41.5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="M25" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>9</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="O25" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="Q25" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="S25" s="9" t="n">
         <v>29.2</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="U25" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5952,58 +6098,59 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="8" t="inlineStr"/>
+      <c r="E26" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="F26" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="G26" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="H26" s="9" t="n">
         <v>9.4</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="I26" s="9" t="n">
         <v>4.2</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>13</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="K26" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>12</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="M26" s="9" t="n">
         <v>23.4</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="O26" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>16</v>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="Q26" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>9</v>
       </c>
-      <c r="R26" s="6" t="n">
+      <c r="S26" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>15</v>
       </c>
-      <c r="T26" s="6" t="n">
+      <c r="U26" s="9" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6023,58 +6170,59 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="F27" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="G27" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="H27" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="I27" s="9" t="n">
         <v>49.5</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="K27" s="9" t="n">
         <v>44.8</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="6" t="n">
+      <c r="M27" s="9" t="n">
         <v>50.4</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="O27" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" s="6" t="n">
+      <c r="Q27" s="9" t="n">
         <v>38.3</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" s="6" t="n">
+      <c r="S27" s="9" t="n">
         <v>26.7</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" s="6" t="n">
+      <c r="U27" s="9" t="n">
         <v>-16.3</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>15</v>
       </c>
     </row>
@@ -6094,58 +6242,59 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="8" t="inlineStr"/>
+      <c r="E28" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="F28" s="9" t="n">
         <v>-2.6</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="G28" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="H28" s="9" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="I28" s="9" t="n">
         <v>27.3</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>4</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="K28" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>10</v>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="M28" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="O28" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>10</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="Q28" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="S28" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>6</v>
       </c>
-      <c r="T28" s="6" t="n">
+      <c r="U28" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6165,58 +6314,59 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="F29" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="G29" s="9" t="n">
         <v>-9</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="H29" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="I29" s="9" t="n">
         <v>-6.6</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>17</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="K29" s="9" t="n">
         <v>41.6</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="M29" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>12</v>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="O29" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>11</v>
       </c>
-      <c r="P29" s="6" t="n">
+      <c r="Q29" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>11</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="S29" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>10</v>
       </c>
-      <c r="T29" s="6" t="n">
+      <c r="U29" s="9" t="n">
         <v>-13.3</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>14</v>
       </c>
     </row>
@@ -6236,58 +6386,59 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="8" t="inlineStr"/>
+      <c r="E30" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="F30" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="G30" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="H30" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="I30" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="K30" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="M30" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>3</v>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="O30" s="9" t="n">
         <v>-13.7</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" s="6" t="n">
+      <c r="Q30" s="9" t="n">
         <v>-15.3</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" s="6" t="n">
+      <c r="S30" s="9" t="n">
         <v>-14.2</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="6" t="n">
+      <c r="U30" s="9" t="n">
         <v>-3.7</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6307,58 +6458,59 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="8" t="inlineStr"/>
+      <c r="E31" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="F31" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="G31" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="H31" s="9" t="n">
         <v>-2.5</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="I31" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="K31" s="9" t="n">
         <v>22.9</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="M31" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="O31" s="9" t="n">
         <v>-14.1</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>3</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="Q31" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="R31" s="6" t="n">
+      <c r="S31" s="9" t="n">
         <v>-23.2</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>2</v>
       </c>
-      <c r="T31" s="6" t="n">
+      <c r="U31" s="9" t="n">
         <v>-4.1</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6378,56 +6530,57 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="8" t="inlineStr"/>
+      <c r="E32" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="F32" s="9" t="n">
         <v>-2.5</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="G32" s="9" t="n">
         <v>3.7</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="H32" s="9" t="n">
         <v>-2.7</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="I32" s="9" t="n">
         <v>-12.8</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="K32" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="6" t="n">
+      <c r="M32" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>2</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="O32" s="9" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" s="6" t="n">
+      <c r="Q32" s="9" t="n">
         <v>-27.4</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>3</v>
       </c>
-      <c r="R32" s="6" t="n">
+      <c r="S32" s="9" t="n">
         <v>-32.9</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>3</v>
       </c>
-      <c r="T32" s="6" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" s="9" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6445,58 +6598,63 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>+5.1% A주 당일 1위·YTD 54.6% 1위. 창신메모리 +12% 신고가가 견인, AI 메모리 슈퍼사이클이 A주로 전이된 하루</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="F33" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="G33" s="9" t="n">
         <v>5.8</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="H33" s="9" t="n">
         <v>6.2</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="I33" s="9" t="n">
         <v>54.6</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="K33" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>5</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="M33" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="O33" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>4</v>
       </c>
-      <c r="P33" s="6" t="n">
+      <c r="Q33" s="9" t="n">
         <v>-36.6</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>12</v>
       </c>
-      <c r="R33" s="6" t="n">
+      <c r="S33" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>4</v>
       </c>
-      <c r="T33" s="6" t="n">
+      <c r="U33" s="9" t="n">
         <v>46.6</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6516,58 +6674,63 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>+3.5%·YTD 38.2% 3위. 반도체·5G와 함께 성장 3형제가 지수 +1.4% 상승분을 대부분 만듦</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="F34" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="G34" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="H34" s="9" t="n">
         <v>6.6</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="I34" s="9" t="n">
         <v>38.2</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>3</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="K34" s="9" t="n">
         <v>52.1</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>4</v>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="M34" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>5</v>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="O34" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>3</v>
       </c>
-      <c r="P34" s="6" t="n">
+      <c r="Q34" s="9" t="n">
         <v>-34</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>11</v>
       </c>
-      <c r="R34" s="6" t="n">
+      <c r="S34" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>8</v>
       </c>
-      <c r="T34" s="6" t="n">
+      <c r="U34" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6587,58 +6750,63 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>+4.0%·주간 +9.6%로 A주 주간 1위. AI연산 인프라 수요가 통신장비까지 확산되는 흐름</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="F35" s="9" t="n">
         <v>9.6</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="G35" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="H35" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="I35" s="9" t="n">
         <v>47.2</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="K35" s="9" t="n">
         <v>99.7</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>2</v>
       </c>
-      <c r="L35" s="6" t="n">
+      <c r="M35" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="O35" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>1</v>
       </c>
-      <c r="P35" s="6" t="n">
+      <c r="Q35" s="9" t="n">
         <v>-37.8</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>13</v>
       </c>
-      <c r="R35" s="6" t="n">
+      <c r="S35" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>6</v>
       </c>
-      <c r="T35" s="6" t="n">
+      <c r="U35" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6658,56 +6826,61 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>+1.7%지만 3개월 -16.1%·YTD -9.1%로 부진 지속. 반등 폭이 성장 3형제 대비 절반 이하</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="F36" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="G36" s="9" t="n">
         <v>9.4</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="H36" s="9" t="n">
         <v>-16.1</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="I36" s="9" t="n">
         <v>-9.1</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>8</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="K36" s="9" t="n">
         <v>56.6</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="M36" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>8</v>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="O36" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>12</v>
       </c>
-      <c r="P36" s="6" t="n">
+      <c r="Q36" s="9" t="n">
         <v>-28.9</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>10</v>
       </c>
-      <c r="R36" s="6" t="n">
+      <c r="S36" s="9" t="n">
         <v>41.9</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>2</v>
       </c>
-      <c r="T36" s="6" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" s="9" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6725,58 +6898,63 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>+1.7%·1개월 +10.4%로 회복 중이나 3개월 -14.9%·YTD -14.6%로 연간 하위권</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="E37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="6" t="n">
+      <c r="F37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="9" t="n">
         <v>10.4</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="H37" s="9" t="n">
         <v>-14.9</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="I37" s="9" t="n">
         <v>-14.6</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>10</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="K37" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>6</v>
       </c>
-      <c r="L37" s="6" t="n">
+      <c r="M37" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>6</v>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="O37" s="9" t="n">
         <v>-10.8</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>6</v>
       </c>
-      <c r="P37" s="6" t="n">
+      <c r="Q37" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>8</v>
       </c>
-      <c r="R37" s="6" t="n">
+      <c r="S37" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>5</v>
       </c>
-      <c r="T37" s="6" t="n">
+      <c r="U37" s="9" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6796,56 +6974,61 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>+2.4%·1개월 +11.2%. 다만 3개월 -20.7%로 A주 최대 낙폭 업종, 감산 기대와 실물 수급의 괴리 구간(추정)</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="F38" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="G38" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="H38" s="9" t="n">
         <v>-20.7</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="I38" s="9" t="n">
         <v>-7.9</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>7</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="K38" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>7</v>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="M38" s="9" t="n">
         <v>-14.9</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>13</v>
       </c>
-      <c r="N38" s="6" t="n">
+      <c r="O38" s="9" t="n">
         <v>-35.2</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>13</v>
       </c>
-      <c r="P38" s="6" t="n">
+      <c r="Q38" s="9" t="n">
         <v>-19.7</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>5</v>
       </c>
-      <c r="R38" s="6" t="n">
+      <c r="S38" s="9" t="n">
         <v>50.7</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" s="9" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6863,58 +7046,63 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>-2.5% 당일 최약·YTD -19.8% 꼴찌. 백주 부진이 소비 약세의 대표 지표로 굳어짐</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
         <v>-2.5</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="F39" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="G39" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="H39" s="9" t="n">
         <v>-4.9</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="I39" s="9" t="n">
         <v>-19.8</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>13</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="K39" s="9" t="n">
         <v>-13</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>13</v>
       </c>
-      <c r="L39" s="6" t="n">
+      <c r="M39" s="9" t="n">
         <v>-11</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>11</v>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="O39" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>10</v>
       </c>
-      <c r="P39" s="6" t="n">
+      <c r="Q39" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>3</v>
       </c>
-      <c r="R39" s="6" t="n">
+      <c r="S39" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>9</v>
       </c>
-      <c r="T39" s="6" t="n">
+      <c r="U39" s="9" t="n">
         <v>336.4</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6934,58 +7122,63 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>-0.1%로 지수 +1.4% 상승장에서 소외. 성장주 랠리에 자금이 은행에서 빠지는 전형적 로테이션</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="F40" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="G40" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="H40" s="9" t="n">
         <v>2.7</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="I40" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>6</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="K40" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="6" t="n">
+      <c r="M40" s="9" t="n">
         <v>42.6</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="O40" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>5</v>
       </c>
-      <c r="P40" s="6" t="n">
+      <c r="Q40" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" s="6" t="n">
+      <c r="S40" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>7</v>
       </c>
-      <c r="T40" s="6" t="n">
+      <c r="U40" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>10</v>
       </c>
     </row>
@@ -7005,58 +7198,63 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>+3.1%·1개월 +19.1%로 1개월 상승률 A주 1위. 금·구리 강세가 미국 금광 신고가와 같은 축</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
         <v>3.1</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="F41" s="9" t="n">
         <v>-3.5</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="G41" s="9" t="n">
         <v>19.1</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="H41" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="I41" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>5</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="K41" s="9" t="n">
         <v>101.1</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" s="6" t="n">
+      <c r="M41" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>7</v>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="O41" s="9" t="n">
         <v>-11.4</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>7</v>
       </c>
-      <c r="P41" s="6" t="n">
+      <c r="Q41" s="9" t="n">
         <v>-21.6</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>6</v>
       </c>
-      <c r="R41" s="6" t="n">
+      <c r="S41" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>3</v>
       </c>
-      <c r="T41" s="6" t="n">
+      <c r="U41" s="9" t="n">
         <v>43.2</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7076,58 +7274,63 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>+0.7%·3개월 -13.5%·YTD -17.7%. 지수 급등일에도 반등 폭이 미미해 정책 기대 소진 구간(추정)</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="F42" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="G42" s="9" t="n">
         <v>6.6</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="H42" s="9" t="n">
         <v>-13.5</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="I42" s="9" t="n">
         <v>-17.7</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>12</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="K42" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>11</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="M42" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>9</v>
       </c>
-      <c r="N42" s="6" t="n">
+      <c r="O42" s="9" t="n">
         <v>-27</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>11</v>
       </c>
-      <c r="P42" s="6" t="n">
+      <c r="Q42" s="9" t="n">
         <v>-10.4</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>2</v>
       </c>
-      <c r="R42" s="6" t="n">
+      <c r="S42" s="9" t="n">
         <v>-6.4</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>11</v>
       </c>
-      <c r="T42" s="6" t="n">
+      <c r="U42" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>11</v>
       </c>
     </row>
@@ -7147,58 +7350,63 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>+0.6%로 지수 +1.4%를 크게 하회. 거래대금 랠리에도 증권주가 안 따라가는 것은 이번 상승의 폭이 좁다는 신호(추정)</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="F43" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="G43" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="H43" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="I43" s="9" t="n">
         <v>-9.699999999999999</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>9</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="K43" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>10</v>
       </c>
-      <c r="L43" s="6" t="n">
+      <c r="M43" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>2</v>
       </c>
-      <c r="N43" s="6" t="n">
+      <c r="O43" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2</v>
       </c>
-      <c r="P43" s="6" t="n">
+      <c r="Q43" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>8</v>
       </c>
-      <c r="R43" s="6" t="n">
+      <c r="S43" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>10</v>
       </c>
-      <c r="T43" s="6" t="n">
+      <c r="U43" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7218,58 +7426,63 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>+1.5%·1개월 +10.2%·3개월 +14.9%로 3개월 기준 A주 1위. 우시앱텍 A +4.8% 사상 최고가가 대표 사례</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="F44" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="G44" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="H44" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="I44" s="9" t="n">
         <v>6.1</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>4</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="K44" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>9</v>
       </c>
-      <c r="L44" s="6" t="n">
+      <c r="M44" s="9" t="n">
         <v>-12.2</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>12</v>
       </c>
-      <c r="N44" s="6" t="n">
+      <c r="O44" s="9" t="n">
         <v>-14</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>8</v>
       </c>
-      <c r="P44" s="6" t="n">
+      <c r="Q44" s="9" t="n">
         <v>-24.5</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>7</v>
       </c>
-      <c r="R44" s="6" t="n">
+      <c r="S44" s="9" t="n">
         <v>-15.7</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>13</v>
       </c>
-      <c r="T44" s="6" t="n">
+      <c r="U44" s="9" t="n">
         <v>62.9</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7289,58 +7502,63 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>-0.9%·YTD -15.9%. 백주와 함께 소비 양대 약세축, 성장 대 소비의 갈림이 전 거래일보다 더 벌어짐</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="F45" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="G45" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="H45" s="9" t="n">
         <v>-4.7</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="I45" s="9" t="n">
         <v>-15.9</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>11</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="K45" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>12</v>
       </c>
-      <c r="L45" s="6" t="n">
+      <c r="M45" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>10</v>
       </c>
-      <c r="N45" s="6" t="n">
+      <c r="O45" s="9" t="n">
         <v>-18.3</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>9</v>
       </c>
-      <c r="P45" s="6" t="n">
+      <c r="Q45" s="9" t="n">
         <v>-13.4</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>4</v>
       </c>
-      <c r="R45" s="6" t="n">
+      <c r="S45" s="9" t="n">
         <v>-7.5</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>12</v>
       </c>
-      <c r="T45" s="6" t="n">
+      <c r="U45" s="9" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7352,7 +7570,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D45">
+  <conditionalFormatting sqref="E2:E45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-2.5"/>
@@ -7364,7 +7582,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E45">
+  <conditionalFormatting sqref="F2:F45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="-3.5"/>
@@ -7376,7 +7594,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F45">
+  <conditionalFormatting sqref="G2:G45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="-9"/>
@@ -7388,7 +7606,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G45">
+  <conditionalFormatting sqref="H2:H45">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="-20.7"/>
@@ -7400,7 +7618,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H45">
+  <conditionalFormatting sqref="I2:I45">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="-19.8"/>
@@ -7412,7 +7630,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J45">
+  <conditionalFormatting sqref="K2:K45">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="-13"/>
@@ -7424,7 +7642,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L45">
+  <conditionalFormatting sqref="M2:M45">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="-14.9"/>
@@ -7436,7 +7654,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N45">
+  <conditionalFormatting sqref="O2:O45">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="-35.2"/>
@@ -7448,7 +7666,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P45">
+  <conditionalFormatting sqref="Q2:Q45">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="-37.8"/>
@@ -7460,7 +7678,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R45">
+  <conditionalFormatting sqref="S2:S45">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="-32.9"/>
@@ -7472,7 +7690,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T45">
+  <conditionalFormatting sqref="U2:U45">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-32.7"/>
@@ -7586,12 +7804,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7639,10 +7857,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7691,10 +7909,10 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7747,15 +7965,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7803,10 +8021,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7859,10 +8077,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7911,10 +8129,10 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7967,15 +8185,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N8" s="8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8019,10 +8237,10 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8075,10 +8293,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8131,15 +8349,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="8" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8187,15 +8405,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8237,15 +8455,15 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8293,15 +8511,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8349,10 +8567,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N15" s="8" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8405,10 +8623,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N16" s="8" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8461,15 +8679,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N17" s="8" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8513,10 +8731,10 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" s="8" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8569,10 +8787,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N19" s="8" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8621,10 +8839,10 @@
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" s="8" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8677,15 +8895,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N21" s="8" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8733,15 +8951,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N22" s="8" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr">
+        <is>
+          <t>세노버스에너지(캐나다 석유·가스 통합기업): 이란·호르무즈 리스크發 유가 강세 수혜</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8789,15 +9011,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N23" s="8" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr">
+        <is>
+          <t>나이키(스포츠 의류·신발 브랜드): 중국 부진·판매 둔화·경영진 리스크로 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8845,15 +9071,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N24" s="8" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8897,15 +9123,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N25" s="8" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr">
+        <is>
+          <t>레볼루션메디슨스(RAS 표적 항암신약 바이오텍): 애널리스트 목표주가 잇단 상향 랠리</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8949,10 +9179,10 @@
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" s="8" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9005,15 +9235,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N27" s="8" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9061,10 +9291,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N28" s="8" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9117,10 +9347,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N29" s="8" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9173,15 +9403,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N30" s="8" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9229,15 +9459,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N31" s="8" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9285,10 +9515,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N32" s="8" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9337,19 +9567,19 @@
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" s="8" t="inlineStr">
+      <c r="N33" s="10" t="inlineStr">
         <is>
           <t>(전일) 폭스코퍼레이션(미디어·방송): FY26 4분기 매출 28%↑, 튜비 최대 실적·월드컵 광고 효과</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9393,10 +9623,10 @@
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" s="8" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9445,15 +9675,15 @@
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" s="8" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9497,15 +9727,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N36" s="8" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9553,15 +9783,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N37" s="8" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9609,10 +9839,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N38" s="8" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9665,15 +9895,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N39" s="8" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9717,10 +9947,14 @@
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" s="8" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr">
+        <is>
+          <t>에쿼티레지덴셜(다세대주택 임대 리츠): 아발론베이와 대등합병 8/17 완료, 8/18부터 Vivmark(VMRK)로 전환 — 신저가는 합병 처리에 따른 기술적 신호</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9773,10 +10007,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N41" s="8" t="inlineStr"/>
+      <c r="N41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9829,10 +10063,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N42" s="8" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9879,15 +10113,15 @@
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" s="8" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9929,15 +10163,15 @@
         </is>
       </c>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" s="8" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9983,15 +10217,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N45" s="8" t="inlineStr"/>
+      <c r="N45" s="10" t="inlineStr">
+        <is>
+          <t>스텔란티스(피아트·크라이슬러·푸조 보유 완성차): 후방카메라 결함 848만대 리콜</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10035,15 +10273,15 @@
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" s="8" t="inlineStr"/>
+      <c r="N46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10087,10 +10325,14 @@
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" s="8" t="inlineStr"/>
+      <c r="N47" s="10" t="inlineStr">
+        <is>
+          <t>퍼미안리소시스(퍼미안분지 셰일원유 생산): 이란·호르무즈 리스크發 유가 강세 수혜</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10143,15 +10385,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N48" s="8" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10195,10 +10437,10 @@
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" s="8" t="inlineStr"/>
+      <c r="N49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10251,19 +10493,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N50" s="8" t="inlineStr">
+      <c r="N50" s="10" t="inlineStr">
         <is>
           <t>(전일) 롤린스(해충방제 서비스): 2분기 EPS 0.32달러로 컨센 하회·경영진 교체 우려로 52주 신저가</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10311,15 +10553,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N51" s="8" t="inlineStr"/>
+      <c r="N51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10363,15 +10605,15 @@
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" s="8" t="inlineStr"/>
+      <c r="N52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10413,10 +10655,10 @@
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" s="8" t="inlineStr"/>
+      <c r="N53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10469,15 +10711,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N54" s="8" t="inlineStr"/>
+      <c r="N54" s="10" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10521,15 +10763,15 @@
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" s="8" t="inlineStr"/>
+      <c r="N55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10573,15 +10815,15 @@
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" s="8" t="inlineStr"/>
+      <c r="N56" s="10" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10625,10 +10867,10 @@
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" s="8" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10679,15 +10921,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N58" s="8" t="inlineStr"/>
+      <c r="N58" s="10" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10735,10 +10977,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N59" s="8" t="inlineStr"/>
+      <c r="N59" s="10" t="inlineStr">
+        <is>
+          <t>무그(항공우주·방산용 정밀 제어장치): 실적 서프라이즈·가이던스 상향 여진 신고가(B주 저유동성 증폭 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10791,19 +11037,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N60" s="8" t="inlineStr">
+      <c r="N60" s="10" t="inlineStr">
         <is>
           <t>(전일) 무그(항공우주·방산 정밀제어시스템): 3분기 실적 호조·FY26 매출 가이던스 44억달러로 상향</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10849,10 +11095,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N61" s="8" t="inlineStr"/>
+      <c r="N61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10901,19 +11147,19 @@
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" s="8" t="inlineStr">
+      <c r="N62" s="10" t="inlineStr">
         <is>
           <t>(전일) 헤클라마이닝(미국 은 광산): 개별 촉매 미확인 — 은·소재 섹터 강세 동조 추정</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10957,15 +11203,19 @@
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" s="8" t="inlineStr"/>
+      <c r="N63" s="10" t="inlineStr">
+        <is>
+          <t>데커스아웃도어(UGG·호카 신발 브랜드): 특별한 뉴스 없음(의류·신발 섹터 전반 약세 동조)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="inlineStr">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11009,10 +11259,10 @@
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" s="8" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11065,10 +11315,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N65" s="8" t="inlineStr"/>
+      <c r="N65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11119,15 +11369,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N66" s="8" t="inlineStr"/>
+      <c r="N66" s="10" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11169,10 +11419,10 @@
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" s="8" t="inlineStr"/>
+      <c r="N67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11225,15 +11475,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N68" s="8" t="inlineStr"/>
+      <c r="N68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11277,10 +11527,14 @@
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" s="8" t="inlineStr"/>
+      <c r="N69" s="10" t="inlineStr">
+        <is>
+          <t>아이엠골드(캐나다 금광 개발·생산): 금값 강세에 금광주 동반 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11333,14 +11587,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N70" s="8" t="inlineStr">
+      <c r="N70" s="10" t="inlineStr">
         <is>
           <t>(전일) 달링인그리디언츠(동물부산물·재생연료 원료): 2분기 사상최대 실적·자사주 10억달러 여진</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11393,15 +11647,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N71" s="8" t="inlineStr"/>
+      <c r="N71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B72" s="7" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11445,15 +11699,15 @@
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" s="8" t="inlineStr"/>
+      <c r="N72" s="10" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B73" s="7" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11497,15 +11751,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N73" s="8" t="inlineStr"/>
+      <c r="N73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="inlineStr">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B74" s="7" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11549,10 +11803,10 @@
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" s="8" t="inlineStr"/>
+      <c r="N74" s="10" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11605,10 +11859,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N75" s="8" t="inlineStr"/>
+      <c r="N75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11661,15 +11915,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N76" s="8" t="inlineStr"/>
+      <c r="N76" s="10" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="inlineStr">
+      <c r="A77" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11713,7 +11967,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N77" s="8" t="inlineStr"/>
+      <c r="N77" s="10" t="inlineStr">
+        <is>
+          <t>서밋테라퓨틱스(항암 이중항체 ivonescimab 개발): 임상 데이터 실망·5억달러 자금조달 무산</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N77"/>
@@ -11819,7 +12077,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11866,14 +12124,14 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr">
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>(전일) 미쓰비시중공업(중공업·방위산업): 방위비 증액 기대와 1분기 실적 호조 지속으로 상승</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11920,14 +12178,14 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) NTT(통신 1위): 개별 뉴스 없음, 금리·방어주 수급에 신고가 진입 추정</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11976,19 +12234,19 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) 닌텐도(게임기·소프트웨어): 인도네시아 스위치·스위치2 발매 추진 보도(지지통신)로 4개월래 최고가</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12036,15 +12294,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>MS&amp;AD(일본 3대 손해보험 그룹): 8/14 1분기 호실적 여진, 보험주 강세 지속</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12086,10 +12348,14 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>혼다(일본 2위 완성차·이륜차 1위): 8/5 1분기 영업익 +117%·가이던스 상향 후 목표주가 상향 랠리 지속</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12142,14 +12408,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>(전일) 리소나홀딩스(대형 은행지주): 정부의 조기 금리인상 지지 보도로 은행주 일제 급등</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12196,14 +12462,14 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>(전일) 테루모(의료기기·수액세트): FY27.3 영업이익 2245억→2575억엔 상향, 1Q 순이익 68%↑</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12254,19 +12520,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="8" t="inlineStr">
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>(전일) 아식스(스포츠용품 제조): 8/14 세션 3거래일째 승계 — 경상익 15% 상향 1890억엔·사상 첫 매출 1조엔 전망, 신규 촉매 없음</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12308,10 +12574,14 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>스미토모부동산(도쿄 오피스 중심 대형 디벨로퍼): 30년물 국채금리 최고치·일본은행 추가 인상 경계로 부동산주 매도</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12364,14 +12634,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="8" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>(전일) 니혼유센(벌크·컨테이너 해운): 해운 3종 동반 강세, 컨테이너 운임 기대(당일 개별뉴스 미확인)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12418,14 +12688,14 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr">
+      <c r="N12" s="10" t="inlineStr">
         <is>
           <t>(전일) 넥슨(온라인게임 퍼블리셔): 8/14 세션 3거래일째 승계 — 2분기 영업익 313억엔으로 컨센 240억엔 상회·특별배당 415엔, 신규 촉매 없음</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12474,10 +12744,10 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12530,19 +12800,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr">
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>(전일) 가와사키기선(컨테이너선 해운): 해운 3종 동반 강세, 컨테이너 운임 기대(당일 개별뉴스 미확인)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12590,7 +12860,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N15" s="8" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>야마하모터(이륜차·선외기 제조): 특별한 뉴스 없음(8월 초 실적 랠리 후 단기 이익실현 추정)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N15"/>
@@ -12696,12 +12970,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12747,15 +13021,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>중지쉬촹(AI 데이터센터용 광트랜시버 1위, 최근 홍콩 상장): AI연산 수요·800G→1.6T 전환 기대, 열관리업체 지분인수 공시</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12801,15 +13079,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>우시앱텍 H주(글로벌 위탁연구개발 1위): 상반기 호실적으로 A주·H주 동시 사상 최고가, 목표주가 상향</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12853,10 +13135,14 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>코스코해운지주 H주(중국 최대 국영 컨테이너 해운): 성수기 물동량·호르무즈 운임 급등, 머스크 가이던스 2차 상향 동조</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12907,19 +13193,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>(전일) CLP홀딩스(홍콩 최대 전력회사, 발전·송배전): 특별한 뉴스 없음(유틸리티 방어주 수급 흐름 추정)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12967,15 +13253,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>콰이쇼우(중국 2위 숏폼동영상·라이브커머스): 전자상거래 거래액 성장 둔화 우려, 8/20 실적발표 앞두고 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13015,10 +13305,10 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13071,19 +13361,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N8" s="8" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>(전일) SITC인터내셔널(아시아 역내 컨테이너 해운): 개별 뉴스 없음, 중간실적 앞둔 해운 강세 동조 추정</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13129,15 +13419,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>OOIL(오리엔트 오버시즈, 컨테이너 해운): 성수기 물동량·호르무즈 리스크로 운임 급등 수혜</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13185,15 +13479,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13237,15 +13531,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="8" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>넥스칩(허페이 파운드리, 디스플레이 구동칩 세계 1위): 반도체 국산화 기대 속 업종 전반 강세(개별 촉매 미확인)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13287,7 +13585,7 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N12"/>
@@ -13393,12 +13691,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13444,15 +13742,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>창신메모리(중국 유일 D램 양산업체): AI발 메모리 슈퍼사이클·D램 가격 급등에 메모리주 전반 급등</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13498,15 +13800,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>우시앱텍 A주(위탁연구개발·위탁생산): 상반기 매출 +39%·순이익 +29% 서프라이즈, 미국 규제 리스크 완화</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13550,15 +13856,19 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>코스코해운지주 A주(중국 최대 국영 컨테이너 해운): 호르무즈 운임 급등·머스크 가이던스 상향에 해운주 동반 급등</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13602,7 +13912,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>화뎬신에너지(화뎬그룹 산하 신재생 발전사): 특별한 뉴스 없음(신재생 발전주 약세 흐름 속 신저가)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N5"/>

--- a/신고신저가_20260818.xlsx
+++ b/신고신저가_20260818.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -618,7 +618,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>💬 ■ 결론: 미국은 지수(-0.5%)보다 내부가 갈렸다 — 신고가 60에 신저가 16(신규 14)인데 신규 신저가 14종 중 7종이 소비재·유통이고 신규 신고가는 에너지·금·은행에 몰림. 반대로 아시아는 D램(창신메모리 +12%)과 해운(호르무즈 운임)이 끌어올린 하루. 네 시장 공통 축은 실물자산·리플레이션이고 공통 반대편은 소비와 금리민감 자산인 국면(추정), 판정은 오늘밤 홈디포부터 열리는 유통 실적 주간이 낸다</t>
+          <t>💬 ■ 결론: 지수만 보면 미국 -0.5%의 조용한 하루지만, 신고/신저 명단은 다른 이야기를 하고 있다. 미국에서 새로 신저가에 들어간 14종 중 7종이 소비재·유통이고, 새 신고가는 에너지·금·은행에 몰렸다. 아시아는 D램과 해운이 끌어올렸다. 네 시장을 관통하는 축은 실물자산·리플레이션이 강하고 소비·금리민감이 밀리는 그림인데(추정), 판정은 오늘 밤 홈디포부터 열리는 유통 실적 주간이 낸다.</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>■ 美(8/17): S&amp;P500 7,745.06 -0.52%·나스닥 26,644.91 -0.32%·다우 53,459.78 -0.51%, 52주 위치 96%. 신고가 60(신규 28)·신저가 16(신규 14)로 전 거래일 81/8 대비 폭이 눈에 띄게 좁아짐. 신규 신저가 명단이 이번 스캔의 본론 — 나이키 -4.0%·데커스 -3.2%·아머스포츠 -0.9%·딕스스포팅 -2.8%·이베이 -2.1%·알트리아 -2.7%에 스텔란티스 -4.5%(카메라 결함 848만대 리콜)까지 소비·유통이 무더기. 여기에 아파트·게이밍 리츠(에쿼티레지덴셜 -3.5%, VICI -1.5%, GLPI -3.0%)가 붙어 소비＋금리민감의 이중 이탈. 반대편 신규 신고가는 에너지(세노버스 +3.6·퍼미안 +3.2·APA +2.7·HF싱클레어 +1.4)와 금광(아이엠골드 +4.1·뉴몬트 +2.2·엘도라도 +1.5·애그니코이글 +1.2), 대형은행(BAC·USB·PNC·M&amp;T·스테이트스트리트·BNY멜론)에 집중. 순강도는 금융 +16(12MF PER 중앙값 15.0, 표본 160/164), 에너지광물 +9(10.9, 22/22), 헬스테크 +4(19.0), 비에너지광물 +4(16.2) / 약세는 소매유통 -2(19.8), 소비내구재 -1(15.9). 다만 ETF는 당일 XLE +1.1%만 뚜렷하고 XLF -1.0%로 순강도와 방향이 엇갈림 — 금융 신고가는 오늘 상승이 아니라 누적 레벨의 잔상. XLK +0.2 / XLC -1.9·XLP -1.6·XLY -1.2·XLRE -1.0. XLE는 주간 +4.0%·YTD 41.9%로 1위 고수</t>
+          <t>■ 美(8/17): 지수 등락폭 -0.5%보다 내부의 균열이 오늘의 본론이다. 신고가 60에 신저가 16으로 전 거래일의 81 대 8보다 폭이 확연히 좁아졌고, 특히 신규 신저가 14종의 절반이 소비·유통이다 — 나이키 -4.0%를 필두로 딕스스포팅·이베이·알트리아 등이 무더기로 들어왔고, 848만대 리콜의 스텔란티스 -4.5%까지 겹쳤다. 아파트·게이밍 리츠 3종도 함께 빠져 소비와 금리민감의 이중 이탈이다. 반대편 신규 신고가는 에너지 4종, 금광 4종, 대형은행 6종에 집중됐다. 다만 은행 신고가는 오늘 오른 결과가 아니라 누적 레벨의 잔상이다 — 당일 섹터 ETF는 에너지 XLE +1.1%만 뚜렷했고 금융 XLF는 오히려 -1.0%였다. XLE는 YTD 41.9%로 1위를 지키고 있다.</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>■ 日(8/17): 닛케이225 69,220.25 +0.74%로 사상 최고치 경신, 5거래일 연속 상승. 신고가 13(신규 3)·신저가 1(신규 1). 신규 신고가는 혼다 +1.8%(8/5 1분기 영업익 +117%·가이던스 상향 이후 목표주가 상향 랠리), MS&amp;AD +1.8%(1분기 호실적 여진), 야마하모터. 업종 ETF는 철강·비철 +4.0% 독주(주간 +8.6%·YTD 59.2% 1위) / 상사·도매 -1.7%·의약 -1.6%·소매 -1.3%. 순강도 소비내구재 +3·운수 +3(상선미쓰이 +2.4·닛폰유센 +1.4·가와사키기선 +1.4로 해운 3사 승계 신고가)·금융 +1. 유일한 신규 신저가가 스미토모부동산 -0.7% — 30년물 국채금리 최고치와 일본은행 추가 인상 경계가 부동산으로 먼저 나옴(부동산 ETF 1개월 -9.0%). 금리 상승이 은행(YTD 49.5%)엔 연료, 부동산엔 독인 구도가 선명</t>
+          <t>■ 日(8/17): 닛케이 69,220으로 0.74% 올라 5거래일 연속 상승하며 사상 최고치를 다시 썼다. 신규 신고가는 혼다·MS&amp;AD·야마하모터 3종으로, 혼다는 8/5 영업익 서프라이즈 이후 목표주가 상향 랠리가 이어지는 중이다. 해운 3사도 신고가를 이어갔고 업종에선 철강·비철 +4.0%가 독주했다. 오늘의 포인트는 유일한 신규 신저가가 스미토모부동산이라는 것 — 30년물 국채금리 최고치와 일본은행 추가 인상 경계가 부동산에서 먼저 터져 나왔다. 같은 금리 상승이 은행에는 연료(YTD 49.5%), 부동산에는 독(1개월 -9.0%)인 구도가 선명하다.</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>■ 홍콩(8/17): 항셍 25,453.23 +1.34%·항셍테크 4,782.03 +1.58%로 반등. 다만 주간은 항셍 -1.9%·항셍테크 -2.8%이고 항셍테크 YTD -12.8%·52주 위치 22%라 중화권 최약 지위는 그대로. 신고가 10(신규 8)·신저가 1. 신규 신고가가 두 갈래 — AI 하드웨어(중지쉬촹 +8.2%, 800G→1.6T 전환 기대와 열관리업체 지분인수 공시 / 넥스칩 +6.0%, 국산화 기대)와 해운(OOIL +7.3%·코스코 H +6.1%·SITC +4.0%), 여기에 위탁연구개발(우시앱텍 H +3.0%·팜아론 +2.6%)이 붙음. 순강도 운수 +3(12MF 10.5, 표본 5/13)·전자기술 +2(21.0, 13/17)·헬스테크 +2(29.6). 유일한 신저가는 콰이쇼우 — 전자상거래 거래액 성장 둔화 우려로 8/20 실적발표 전 신저가</t>
+          <t>■ 홍콩(8/17): 항셍 +1.34%로 반등했지만 주간 -1.9%에 항셍테크 YTD -12.8%로 중화권 최약 지위는 그대로다. 신규 신고가 8종이 두 갈래로 갈린다 — 한쪽은 AI 하드웨어로, 광모듈 중지쉬촹이 1.6T 전환 기대와 열관리업체 지분인수 공시로 +8.2% 올랐고 넥스칩 등이 뒤따랐다. 다른 쪽은 해운으로 OOIL +7.3% 등 3종이 들어왔고, 위탁연구개발 2종(우시앱텍 H 등)도 붙었다. 유일한 신저가는 콰이쇼우 — 8/20 실적발표를 앞두고 전자상거래 성장 둔화 우려가 눌렀다.</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>■ 中(8/17): 상해종합 3,982.65 +1.41%·CSI300 4,741.10 +1.61%로 사흘 보합을 깨고 급등, 상해종합은 4,000선 목전. 신고가 3(전부 신규)·신저가 1. 창신메모리 +12.0%가 이날의 중심 — AI발 메모리 슈퍼사이클과 D램 가격 급등이 중국 유일 D램 양산업체로 직결. 우시앱텍 A +4.8%(상반기 매출 +39%·순이익 +29%), 코스코 A +3.8%로 A주·H주가 같은 종목에서 동시에 신고가를 낸 것이 특징. 업종 ETF는 반도체 +5.1%(YTD 54.6% 1위)·5G통신 +4.0%(47.2%)·테크 +3.5%(38.2%)·유색금속 +3.1%(1개월 +19.1%) / 백주 -2.5%(YTD -19.8% 꼴찌)·소비 -0.9%로 성장 대 소비의 갈림이 전 거래일보다 더 벌어짐. 순강도는 표본이 얇아(전자기술 12MF 38/72) 밸류 절대수준 인용은 보류</t>
+          <t>■ 中(8/17): 상해종합이 +1.41%로 사흘 보합을 깨고 4,000선 목전까지 왔다. 중심은 창신메모리 +12.0% — AI발 D램 가격 급등이 중국 유일의 D램 양산업체로 직결됐고, A주 반도체 ETF도 +5.1%로 YTD 1위다. 반대편에선 백주 -2.5%(YTD 꼴찌)로 성장 대 소비의 갈림이 전 거래일보다 더 벌어졌다. 우시앱텍과 코스코가 A주·H주 양쪽에서 동시에 신고가를 낸 것도 오늘의 특징이다. 순강도의 밸류 수치는 12MF 표본이 얇아 인용을 보류한다.</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>■ 체크: ①8/18(화) 홈디포 컨센 EPS 4.73달러 — 신규 신저가 14종 중 7종이 소비·유통에 몰린 상태에서 나오는 첫 실물 확인, 8/19 타깃·8/20 월마트로 이어지는 주간의 방향타 ②메모리·광모듈 축의 지속성 — 창신메모리 +12%·중지쉬촹 +8.2%·A주 반도체 ETF +5.1%가 하루짜리 가격 뉴스인지 8/26 엔비디아까지 이어지는 사이클 확인인지, A주 반도체 ETF의 1개월 조정 여부가 1차 단서 ③호르무즈 운임 — 해운주가 미·일·중·홍콩 4개 시장에서 동시 신고가를 낸 만큼 이미 컨센이나, 운임 상승이 인플레로 되돌아오면 8/19 FOMC 회의록·금리 경로에 역풍이라 양방향</t>
+          <t>■ 체크: ①오늘 밤 홈디포 실적(컨센 EPS 4.73달러) — 신저가 명단의 소비재 쏠림이 실제 실적 악화인지 확인하는 첫 관문이고, 8/19 타깃·8/20 월마트로 이어지는 유통 주간의 방향타다 ②창신메모리·중지쉬촹의 메모리·광모듈 축이 하루짜리 가격 뉴스인지 8/26 엔비디아 실적까지 이어지는 사이클 확인인지 — A주 반도체 ETF의 조정 여부가 1차 단서 ③해운이 네 시장 동시 신고가를 낼 만큼 호르무즈 운임은 이미 컨센이다 — 운임발 인플레가 8/19 FOMC 회의록의 금리 경로에 역풍이 되면 양방향으로 갈린다.</t>
         </is>
       </c>
     </row>
@@ -678,12 +678,22 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ 참고: 08:07 KST 실행 — 미국은 8/17(월) ET 16:00 마감분으로 약 3시간 전 확정, 일본·홍콩·중국A는 8/17 마감분(오늘 개장 전)이라 전 시장 정상 갱신. 스크립트가 만든 index CSV의 닛케이225·KOSPI는 8/14로 갱신이 밀려 있어 닛케이 8/17 종가는 별도 확인값(69,220.25 +0.74%)을 사용. ETF 44/44·지수 8/8 수집 정상, 12MF PER은 TradingView 선행 배수. 에쿼티레지덴셜 신저가는 아발론베이와의 대등합병이 8/17 완료돼 8/18부터 Vivmark(VMRK)로 전환되는 데 따른 처리 신호로 판단, 펀더멘털 악화 신호로 읽지 말 것. 회사PC 자격증명 부재로 vault pull 실패해 텔레그램 적재분 미사용</t>
-        </is>
-      </c>
+          <t>■ 배울점: 지수는 평균이라 갈림을 숨긴다. 오늘 미국 지수 -0.5%는 밋밋했지만, 신규 신저가 14종 중 7종이 소비재라는 명단의 "구성"은 특정 섹터의 조용한 이탈을 먼저 말하고 있었다. 신고/신저 스크리닝의 존재 이유가 이것이다 — 방향이 갈리는 날일수록 지수가 아니라 명단의 구성을 봐야 하고, 그 쏠림이 실적 시즌 직전에 나오면 시장이 미리 답안을 적는 중일 가능성이 높다. 이번 주 유통 실적 발표가 그 답안지 채점이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>■ 참고: 08:07 KST 실행으로 미국은 8/17(월) 마감 약 3시간 후 확정치, 일본·홍콩·중국A는 8/17 마감분이라 전 시장 정상 갱신. index CSV의 닛케이·KOSPI가 8/14에서 멈춰 있어 닛케이 종가는 별도 확인값(69,220.25 +0.74%)을 사용. ETF 44/44·지수 8/8 수집 정상, PER은 TradingView 12MF 선행 배수. 에쿼티레지덴셜의 신저가는 아발론베이와의 합병 완료로 8/18부터 Vivmark(VMRK)로 전환되는 데 따른 처리 신호이므로 펀더멘털 악화로 읽지 말 것. 회사PC 자격증명 문제로 vault pull이 실패해 텔레그램 적재분은 미사용.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>

--- a/신고신저가_20260818.xlsx
+++ b/신고신저가_20260818.xlsx
@@ -678,7 +678,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ 배울점: 지수는 평균이라 갈림을 숨긴다. 오늘 미국 지수 -0.5%는 밋밋했지만, 신규 신저가 14종 중 7종이 소비재라는 명단의 "구성"은 특정 섹터의 조용한 이탈을 먼저 말하고 있었다. 신고/신저 스크리닝의 존재 이유가 이것이다 — 방향이 갈리는 날일수록 지수가 아니라 명단의 구성을 봐야 하고, 그 쏠림이 실적 시즌 직전에 나오면 시장이 미리 답안을 적는 중일 가능성이 높다. 이번 주 유통 실적 발표가 그 답안지 채점이다.</t>
+          <t>■ 배울점: 오늘 일본이 좋은 교재다 — 같은 재료(장기금리 상승)가 은행은 올리고 부동산은 내렸다. 은행이 오르는 로직: 금리가 오르면 대출·채권 운용수익률이 먼저 오르고 예금금리는 천천히 따라와 이자마진이 벌어지는데, 이 증분에는 비용이 거의 붙지 않아 그대로 이익이 된다(은행 YTD 49.5%). 부동산이 내리는 로직: 차입이 큰 사업이라 이자비용이 커지는 데다, 자산가치를 매기는 할인율이 올라 같은 임대수익도 더 낮게 평가된다 — 그래서 신저가가 실적 악화 종목이 아니라 스미토모부동산에서 나왔고, 부동산 ETF는 한 달간 -9.0%다. 요령: 재료를 들으면 "누가 수혜냐"를 외우지 말고, 그 재료가 이익(P·Q·C)을 건드리는지 멀티플(할인율)을 건드리는지 경로를 따라가면 오르내림의 방향과 순서가 나온다.</t>
         </is>
       </c>
     </row>
